--- a/data_1.xlsx
+++ b/data_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Eurostat\ESTP\ESTP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CCE2FEF-6CAC-4252-9D6D-7D2CE6BA7AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677F7191-FD73-43CC-9B2E-0AF521BAF93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A5FDF58C-5098-40E2-80F2-75779B8FB9E9}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="27">
   <si>
     <t xml:space="preserve">Camplet </t>
   </si>
@@ -163,7 +163,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="5"/>
+      <color rgb="FFFFC000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -302,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -316,7 +316,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -343,10 +342,7 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -686,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12399938-0FF5-4B9D-875D-7E95B451EB5D}">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="6" max="6" width="18.86328125" bestFit="1" customWidth="1"/>
@@ -694,12 +690,12 @@
     <col min="11" max="11" width="15.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -707,278 +703,277 @@
         <v>0.9681999</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
         <v>0.86008430000000002</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="11"/>
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="4" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4">
         <v>0.65065609999999996</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5">
         <v>0.93508389999999997</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="4">
         <v>2.0341069999999999E-27</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <v>0.9681999</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <v>0.86008430000000002</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="15">
         <v>0.65065609999999996</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="16">
         <v>0.93508389999999997</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="17">
         <v>2.0341069999999999E-27</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <v>0.99966730000000004</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>0.83453250000000001</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="17">
         <v>8.9382679999999996E-4</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>0.99769660000000004</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="17">
         <v>1.3600599999999999E-29</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <v>0.99966730000000004</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <v>0.99963959999999996</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <v>0.9655009</v>
       </c>
-      <c r="I8" s="16">
-        <v>1</v>
-      </c>
-      <c r="J8" s="17">
+      <c r="I8" s="15">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16">
         <v>0.99858990000000003</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K8" s="17">
         <v>9.1302109999999997E-27</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <v>0.83453250000000001</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <v>0.99999979999999999</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>0.68460750000000004</v>
       </c>
-      <c r="I9" s="16">
-        <v>1</v>
-      </c>
-      <c r="J9" s="17">
+      <c r="I9" s="15">
+        <v>1</v>
+      </c>
+      <c r="J9" s="16">
         <v>0.99739489999999997</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="15">
         <v>0.99995889999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10">
         <v>8.9382679999999996E-4</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="16">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16">
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15">
         <v>0.98510660000000005</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="15">
         <v>0.31481749999999997</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <v>0.99998319999999996</v>
       </c>
-      <c r="K10" s="18">
+      <c r="K10" s="17">
         <v>3.3262040000000001E-34</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <v>0.99769660000000004</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <v>0.99804669999999995</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>0.94348030000000005</v>
       </c>
-      <c r="I11" s="16">
-        <v>1</v>
-      </c>
-      <c r="J11" s="17">
+      <c r="I11" s="15">
+        <v>1</v>
+      </c>
+      <c r="J11" s="16">
         <v>0.99997409999999998</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="15">
         <v>0.75148159999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="4">
         <v>1.3600599999999999E-29</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <v>0.97501720000000003</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <v>0.8023074</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="15">
         <v>0.1489859</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="16">
         <v>0.99807389999999996</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="17">
         <v>1.739317E-32</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <v>0.99999009999999999</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <v>0.97282380000000002</v>
       </c>
-      <c r="I13" s="16">
-        <v>1</v>
-      </c>
-      <c r="J13" s="17">
+      <c r="I13" s="15">
+        <v>1</v>
+      </c>
+      <c r="J13" s="16">
         <v>0.99922949999999999</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="15">
         <v>0.83620819999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B14">
         <v>0.99963959999999996</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="11"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,7 +981,7 @@
         <v>0.9655009</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1276,14 +1271,14 @@
       <c r="B3">
         <v>0.6796065</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="11"/>
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1294,20 +1289,20 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="9"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -1316,12 +1311,12 @@
       <c r="B5">
         <v>0.82970390000000005</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="10"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -1330,23 +1325,23 @@
       <c r="B6">
         <v>0.24827640000000001</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <f t="array" ref="G6:K6">TRANSPOSE(B2:B6)</f>
         <v>0.93060699999999996</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <v>0.6796065</v>
       </c>
-      <c r="I6" s="16">
-        <v>1</v>
-      </c>
-      <c r="J6" s="17">
+      <c r="I6" s="15">
+        <v>1</v>
+      </c>
+      <c r="J6" s="16">
         <v>0.82970390000000005</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="18">
         <v>0.24827640000000001</v>
       </c>
     </row>
@@ -1354,23 +1349,23 @@
       <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <f t="array" ref="G7:K7">TRANSPOSE(B8:B12)</f>
         <v>0.86027699999999996</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>0.69606060000000003</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0.44479540000000001</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>0.66204989999999997</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="18">
         <v>0.12406159999999999</v>
       </c>
     </row>
@@ -1381,23 +1376,23 @@
       <c r="B8">
         <v>0.86027699999999996</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <f t="array" ref="G8:K8">TRANSPOSE(B14:B18)</f>
         <v>0.99431230000000004</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <v>0.79373039999999995</v>
       </c>
-      <c r="I8" s="16">
-        <v>1</v>
-      </c>
-      <c r="J8" s="17">
+      <c r="I8" s="15">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16">
         <v>0.85233890000000001</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="18">
         <v>0.12257709999999999</v>
       </c>
     </row>
@@ -1408,23 +1403,23 @@
       <c r="B9">
         <v>0.69606060000000003</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <f t="array" ref="G9:K9">TRANSPOSE(B20:B24)</f>
         <v>0.99986370000000002</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>0.45215909999999998</v>
       </c>
-      <c r="I9" s="16">
-        <v>1</v>
-      </c>
-      <c r="J9" s="17">
+      <c r="I9" s="15">
+        <v>1</v>
+      </c>
+      <c r="J9" s="16">
         <v>0.99020560000000002</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="18">
         <v>0.99997539999999996</v>
       </c>
     </row>
@@ -1435,23 +1430,23 @@
       <c r="B10">
         <v>0.44479540000000001</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <f t="array" ref="G10:K10">TRANSPOSE(B26:B30)</f>
         <v>0.99998160000000003</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <v>0.83121630000000002</v>
       </c>
-      <c r="I10" s="16">
-        <v>1</v>
-      </c>
-      <c r="J10" s="17">
+      <c r="I10" s="15">
+        <v>1</v>
+      </c>
+      <c r="J10" s="16">
         <v>0.91414410000000001</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="18">
         <v>0.1957972</v>
       </c>
     </row>
@@ -1462,23 +1457,23 @@
       <c r="B11">
         <v>0.66204989999999997</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <f t="array" ref="G11:K11">TRANSPOSE(B32:B36)</f>
         <v>0.43817149999999999</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>0.43598690000000001</v>
       </c>
-      <c r="I11" s="16">
-        <v>1</v>
-      </c>
-      <c r="J11" s="17">
+      <c r="I11" s="15">
+        <v>1</v>
+      </c>
+      <c r="J11" s="16">
         <v>0.72704239999999998</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="18">
         <v>0.33244980000000002</v>
       </c>
     </row>
@@ -1489,23 +1484,23 @@
       <c r="B12">
         <v>0.12406159999999999</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <f t="array" ref="G12:K12">TRANSPOSE(B38:B42)</f>
         <v>0.94606509999999999</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <v>0.76371610000000001</v>
       </c>
-      <c r="I12" s="16">
-        <v>1</v>
-      </c>
-      <c r="J12" s="17">
+      <c r="I12" s="15">
+        <v>1</v>
+      </c>
+      <c r="J12" s="16">
         <v>0.45453700000000002</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="18">
         <v>0.13576299999999999</v>
       </c>
     </row>
@@ -1513,23 +1508,23 @@
       <c r="A13" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <f t="array" ref="G13:K13">TRANSPOSE(B44:B48)</f>
         <v>0.89964169999999999</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <v>0.71211530000000001</v>
       </c>
-      <c r="I13" s="16">
-        <v>1</v>
-      </c>
-      <c r="J13" s="17">
+      <c r="I13" s="15">
+        <v>1</v>
+      </c>
+      <c r="J13" s="16">
         <v>0.91207380000000005</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="18">
         <v>0.70230090000000001</v>
       </c>
     </row>
@@ -1540,12 +1535,12 @@
       <c r="B14">
         <v>0.99431230000000004</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="11"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
@@ -1812,558 +1807,857 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB998DD-7076-4A95-ACFE-5C8B5AC932FF}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="6" max="6" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="1"/>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4">
-        <v>3.1179210000000002E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="1">
+        <v>0.93060699999999996</v>
+      </c>
+      <c r="N2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.93060699999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
-        <v>0.13816419999999999</v>
-      </c>
-      <c r="F3" s="12"/>
+      <c r="B3" s="1">
+        <v>0.6796065</v>
+      </c>
+      <c r="F3" s="11"/>
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="N3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.6796065</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>1.071181E-2</v>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="15" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K4" s="8"/>
+      <c r="N4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>1.163297E-4</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="B5" s="1">
+        <v>0.82970390000000005</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K5" s="9"/>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0.82970390000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4">
-        <v>7.7100340000000001E-45</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="B6" s="1">
+        <v>0.24827640000000001</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="18">
         <f t="array" ref="G6:K6">TRANSPOSE(B2:B6)</f>
-        <v>3.1179210000000002E-5</v>
-      </c>
-      <c r="H6" s="22">
-        <v>0.13816419999999999</v>
+        <v>0.93060699999999996</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0.6796065</v>
       </c>
       <c r="I6" s="18">
-        <v>1.071181E-2</v>
-      </c>
-      <c r="J6" s="20">
-        <v>1.163297E-4</v>
+        <v>1</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.82970390000000005</v>
       </c>
       <c r="K6" s="18">
-        <v>7.7100340000000001E-45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+        <v>0.24827640000000001</v>
+      </c>
+      <c r="N6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.24827640000000001</v>
+      </c>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="B7" s="1"/>
+      <c r="F7" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="18">
         <f t="array" ref="G7:K7">TRANSPOSE(B8:B12)</f>
-        <v>1.8324179999999998E-5</v>
-      </c>
-      <c r="H7" s="16">
-        <v>0.26905250000000003</v>
+        <v>0.86027699999999996</v>
+      </c>
+      <c r="H7" s="15">
+        <v>0.69606060000000003</v>
       </c>
       <c r="I7" s="18">
-        <v>0</v>
-      </c>
-      <c r="J7" s="21">
-        <v>0.1197018</v>
-      </c>
-      <c r="K7" s="18">
-        <v>6.0776260000000002E-25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+        <v>0.44479540000000001</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0.66204989999999997</v>
+      </c>
+      <c r="K7" s="20">
+        <v>0.12406159999999999</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4">
-        <v>1.8324179999999998E-5</v>
-      </c>
-      <c r="F8" s="10" t="s">
+      <c r="B8" s="1">
+        <v>0.86027699999999996</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <f t="array" ref="G8:K8">TRANSPOSE(B14:B18)</f>
-        <v>0.99998229999999999</v>
-      </c>
-      <c r="H8" s="16">
-        <v>0.91405250000000005</v>
-      </c>
-      <c r="I8" s="16">
-        <v>1</v>
-      </c>
-      <c r="J8" s="17">
-        <v>0.99994769999999999</v>
-      </c>
-      <c r="K8" s="18">
-        <v>2.7679700000000001E-46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+        <v>0.99431230000000004</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.79373039999999995</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16">
+        <v>0.85233890000000001</v>
+      </c>
+      <c r="K8" s="20">
+        <v>0.12257709999999999</v>
+      </c>
+      <c r="N8" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.86027699999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>0.26905250000000003</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="B9" s="1">
+        <v>0.69606060000000003</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <f t="array" ref="G9:K9">TRANSPOSE(B20:B24)</f>
-        <v>0.99999930000000004</v>
-      </c>
-      <c r="H9" s="16">
-        <v>0.51405970000000001</v>
-      </c>
-      <c r="I9" s="16">
-        <v>1</v>
-      </c>
-      <c r="J9" s="17">
-        <v>0.9685918</v>
-      </c>
-      <c r="K9" s="19">
-        <v>0.99608680000000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+        <v>0.99986370000000002</v>
+      </c>
+      <c r="H9" s="15">
+        <v>0.45215909999999998</v>
+      </c>
+      <c r="I9" s="15">
+        <v>1</v>
+      </c>
+      <c r="J9" s="16">
+        <v>0.99020560000000002</v>
+      </c>
+      <c r="K9" s="18">
+        <v>0.99997539999999996</v>
+      </c>
+      <c r="N9" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0.69606060000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="B10" s="1">
+        <v>0.44479540000000001</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <f t="array" ref="G10:K10">TRANSPOSE(B26:B30)</f>
-        <v>1</v>
-      </c>
-      <c r="H10" s="16">
-        <v>0.84522839999999999</v>
-      </c>
-      <c r="I10" s="16">
-        <v>1</v>
-      </c>
-      <c r="J10" s="17">
-        <v>0.99995579999999995</v>
-      </c>
-      <c r="K10" s="18">
-        <v>9.5658310000000005E-45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+        <v>0.99998160000000003</v>
+      </c>
+      <c r="H10" s="15">
+        <v>0.83121630000000002</v>
+      </c>
+      <c r="I10" s="15">
+        <v>1</v>
+      </c>
+      <c r="J10" s="16">
+        <v>0.91414410000000001</v>
+      </c>
+      <c r="K10" s="20">
+        <v>0.1957972</v>
+      </c>
+      <c r="N10" t="s">
+        <v>10</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.44479540000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>0.1197018</v>
-      </c>
-      <c r="F11" s="10" t="s">
+      <c r="B11" s="1">
+        <v>0.66204989999999997</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <f t="array" ref="G11:K11">TRANSPOSE(B32:B36)</f>
-        <v>0.98142479999999999</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.83818839999999994</v>
-      </c>
-      <c r="I11" s="16">
-        <v>1</v>
-      </c>
-      <c r="J11" s="17">
-        <v>0.99681790000000003</v>
+        <v>0.43817149999999999</v>
+      </c>
+      <c r="H11" s="15">
+        <v>0.43598690000000001</v>
+      </c>
+      <c r="I11" s="15">
+        <v>1</v>
+      </c>
+      <c r="J11" s="16">
+        <v>0.72704239999999998</v>
       </c>
       <c r="K11" s="18">
-        <v>5.1275009999999996E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+        <v>0.33244980000000002</v>
+      </c>
+      <c r="N11" t="s">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0.66204989999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4">
-        <v>6.0776260000000002E-25</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="B12" s="1">
+        <v>0.12406159999999999</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <f t="array" ref="G12:K12">TRANSPOSE(B38:B42)</f>
-        <v>0.98320660000000004</v>
-      </c>
-      <c r="H12" s="16">
-        <v>0.93638460000000001</v>
+        <v>0.94606509999999999</v>
+      </c>
+      <c r="H12" s="15">
+        <v>0.76371610000000001</v>
       </c>
       <c r="I12" s="18">
-        <v>1.251238E-2</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0.99887230000000005</v>
-      </c>
-      <c r="K12" s="18">
-        <v>3.3039119999999998E-60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="J12" s="16">
+        <v>0.45453700000000002</v>
+      </c>
+      <c r="K12" s="20">
+        <v>0.13576299999999999</v>
+      </c>
+      <c r="N12" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0.12406159999999999</v>
+      </c>
+      <c r="P12" s="4"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="B13" s="1"/>
+      <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <f t="array" ref="G13:K13">TRANSPOSE(B44:B48)</f>
-        <v>0.95352749999999997</v>
-      </c>
-      <c r="H13" s="16">
-        <v>0.79810389999999998</v>
-      </c>
-      <c r="I13" s="16">
-        <v>0.22964180000000001</v>
-      </c>
-      <c r="J13" s="17">
-        <v>0.99844180000000005</v>
+        <v>0.89964169999999999</v>
+      </c>
+      <c r="H13" s="15">
+        <v>0.71211530000000001</v>
+      </c>
+      <c r="I13" s="15">
+        <v>1</v>
+      </c>
+      <c r="J13" s="16">
+        <v>0.91207380000000005</v>
       </c>
       <c r="K13" s="18">
-        <v>1.714555E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>0.70230090000000001</v>
+      </c>
+      <c r="N13" t="s">
+        <v>2</v>
+      </c>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14">
-        <v>0.99998229999999999</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="11"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B14" s="1">
+        <v>0.99431230000000004</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="10"/>
+      <c r="N14" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0.99431230000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15">
-        <v>0.91405250000000005</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B15" s="1">
+        <v>0.79373039999999995</v>
+      </c>
+      <c r="N15" t="s">
+        <v>9</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0.79373039999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>10</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" t="s">
+        <v>10</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>11</v>
       </c>
-      <c r="B17">
-        <v>0.99994769999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B17" s="1">
+        <v>0.85233890000000001</v>
+      </c>
+      <c r="N17" t="s">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0.85233890000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="4">
-        <v>2.7679700000000001E-46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="1">
+        <v>0.12257709999999999</v>
+      </c>
+      <c r="N18" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0.12257709999999999</v>
+      </c>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B19" s="1"/>
+      <c r="N19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20">
-        <v>0.99999930000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B20" s="1">
+        <v>0.99986370000000002</v>
+      </c>
+      <c r="N20" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0.99986370000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>9</v>
       </c>
-      <c r="B21">
-        <v>0.51405970000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B21" s="1">
+        <v>0.45215909999999998</v>
+      </c>
+      <c r="N21" t="s">
+        <v>9</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0.45215909999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>10</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>11</v>
       </c>
-      <c r="B23">
-        <v>0.9685918</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B23" s="1">
+        <v>0.99020560000000002</v>
+      </c>
+      <c r="N23" t="s">
+        <v>11</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0.99020560000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>12</v>
       </c>
-      <c r="B24">
-        <v>0.99608680000000005</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B24" s="1">
+        <v>0.99997539999999996</v>
+      </c>
+      <c r="N24" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0.99997539999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B25" s="1"/>
+      <c r="N25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>8</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" s="1">
+        <v>0.99998160000000003</v>
+      </c>
+      <c r="N26" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0.99998160000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>9</v>
       </c>
-      <c r="B27">
-        <v>0.84522839999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B27" s="1">
+        <v>0.83121630000000002</v>
+      </c>
+      <c r="N27" t="s">
+        <v>9</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0.83121630000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>10</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="N28" t="s">
+        <v>10</v>
+      </c>
+      <c r="O28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>11</v>
       </c>
-      <c r="B29">
-        <v>0.99995579999999995</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B29" s="1">
+        <v>0.91414410000000001</v>
+      </c>
+      <c r="N29" t="s">
+        <v>11</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0.91414410000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="4">
-        <v>9.5658310000000005E-45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B30" s="1">
+        <v>0.1957972</v>
+      </c>
+      <c r="N30" t="s">
+        <v>12</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0.1957972</v>
+      </c>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B31" s="1"/>
+      <c r="N31" t="s">
+        <v>5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>8</v>
       </c>
-      <c r="B32">
-        <v>0.98142479999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B32" s="1">
+        <v>0.43817149999999999</v>
+      </c>
+      <c r="N32" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0.43817149999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>9</v>
       </c>
-      <c r="B33">
-        <v>0.83818839999999994</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B33" s="1">
+        <v>0.43598690000000001</v>
+      </c>
+      <c r="N33" t="s">
+        <v>9</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0.43598690000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>10</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="N34" t="s">
+        <v>10</v>
+      </c>
+      <c r="O34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>11</v>
       </c>
-      <c r="B35">
-        <v>0.99681790000000003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B35" s="1">
+        <v>0.72704239999999998</v>
+      </c>
+      <c r="N35" t="s">
+        <v>11</v>
+      </c>
+      <c r="O35" s="1">
+        <v>0.72704239999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>12</v>
       </c>
-      <c r="B36">
-        <v>5.1275009999999996E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B36" s="1">
+        <v>0.33244980000000002</v>
+      </c>
+      <c r="N36" t="s">
+        <v>12</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0.33244980000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B37" s="1"/>
+      <c r="N37" t="s">
+        <v>6</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>8</v>
       </c>
-      <c r="B38">
-        <v>0.98320660000000004</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B38" s="1">
+        <v>0.94606509999999999</v>
+      </c>
+      <c r="N38" t="s">
+        <v>8</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0.94606509999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="B39">
-        <v>0.93638460000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B39" s="1">
+        <v>0.76371610000000001</v>
+      </c>
+      <c r="N39" t="s">
+        <v>9</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0.76371610000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>10</v>
       </c>
-      <c r="B40">
-        <v>1.251238E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="N40" t="s">
+        <v>10</v>
+      </c>
+      <c r="O40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>11</v>
       </c>
-      <c r="B41">
-        <v>0.99887230000000005</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B41" s="1">
+        <v>0.45453700000000002</v>
+      </c>
+      <c r="N41" t="s">
+        <v>11</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0.45453700000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="4">
-        <v>3.3039119999999998E-60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B42" s="1">
+        <v>0.13576299999999999</v>
+      </c>
+      <c r="N42" t="s">
+        <v>12</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0.13576299999999999</v>
+      </c>
+      <c r="P42" s="4"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B43" s="1"/>
+      <c r="N43" t="s">
+        <v>7</v>
+      </c>
+      <c r="O43" s="1"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>8</v>
       </c>
-      <c r="B44">
-        <v>0.95352749999999997</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B44" s="1">
+        <v>0.89964169999999999</v>
+      </c>
+      <c r="N44" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0.89964169999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>9</v>
       </c>
-      <c r="B45">
-        <v>0.79810389999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B45" s="1">
+        <v>0.71211530000000001</v>
+      </c>
+      <c r="N45" t="s">
+        <v>9</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0.71211530000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>10</v>
       </c>
-      <c r="B46">
-        <v>0.22964180000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="N46" t="s">
+        <v>10</v>
+      </c>
+      <c r="O46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>11</v>
       </c>
-      <c r="B47">
-        <v>0.99844180000000005</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B47" s="1">
+        <v>0.91207380000000005</v>
+      </c>
+      <c r="N47" t="s">
+        <v>11</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0.91207380000000005</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>12</v>
       </c>
-      <c r="B48">
-        <v>1.714555E-3</v>
-      </c>
+      <c r="B48" s="1">
+        <v>0.70230090000000001</v>
+      </c>
+      <c r="N48" t="s">
+        <v>12</v>
+      </c>
+      <c r="O48" s="1">
+        <v>0.70230090000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B49" s="2"/>
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B50" s="3"/>
+      <c r="O50" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>